--- a/diseases/d124/2005-2009.xlsx
+++ b/diseases/d124/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>18</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.03761626246320816</v>
       </c>
@@ -1605,9 +1599,6 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.02163039537767103</v>
       </c>
@@ -2297,9 +2288,6 @@
       <c r="O11" t="n">
         <v>3</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.05718553388986295</v>
       </c>
@@ -2841,9 +2829,6 @@
       <c r="O14" t="n">
         <v>13</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.02716730066787256</v>
       </c>
@@ -2989,9 +2974,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3681,9 +3663,6 @@
       <c r="O19" t="n">
         <v>1</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -4225,9 +4204,6 @@
       <c r="O22" t="n">
         <v>17</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.03552647010414104</v>
       </c>
@@ -4373,9 +4349,6 @@
       <c r="O23" t="n">
         <v>3</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.06489118613301309</v>
       </c>
@@ -4917,9 +4890,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5461,9 +5431,6 @@
       <c r="O29" t="n">
         <v>19</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.03970605482227528</v>
       </c>
@@ -5609,9 +5576,6 @@
       <c r="O30" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.04326079075534206</v>
       </c>
@@ -6301,9 +6265,6 @@
       <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -6845,9 +6806,6 @@
       <c r="O37" t="n">
         <v>29</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.06060397841294649</v>
       </c>
@@ -6993,9 +6951,6 @@
       <c r="O38" t="n">
         <v>3</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.06489118613301309</v>
       </c>
@@ -7685,9 +7640,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -8229,9 +8181,6 @@
       <c r="O45" t="n">
         <v>15</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.0313468853860068</v>
       </c>
@@ -8377,9 +8326,6 @@
       <c r="O46" t="n">
         <v>2</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.04326079075534206</v>
       </c>
@@ -9069,9 +9015,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -9613,9 +9556,6 @@
       <c r="O53" t="n">
         <v>15</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.0313468853860068</v>
       </c>
@@ -9761,9 +9701,6 @@
       <c r="O54" t="n">
         <v>5</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.1081519768883552</v>
       </c>
@@ -10453,9 +10390,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -10997,9 +10931,6 @@
       <c r="O61" t="n">
         <v>11</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.02298771594973832</v>
       </c>
@@ -11145,9 +11076,6 @@
       <c r="O62" t="n">
         <v>3</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.06489118613301309</v>
       </c>
@@ -11837,9 +11765,6 @@
       <c r="O66" t="n">
         <v>1</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -12381,9 +12306,6 @@
       <c r="O69" t="n">
         <v>19</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.03970605482227528</v>
       </c>
@@ -12529,9 +12451,6 @@
       <c r="O70" t="n">
         <v>2</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.04326079075534206</v>
       </c>
@@ -13221,9 +13140,6 @@
       <c r="O74" t="n">
         <v>1</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -13765,9 +13681,6 @@
       <c r="O77" t="n">
         <v>12</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.02507750830880544</v>
       </c>
@@ -13913,9 +13826,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -14605,9 +14515,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -15149,9 +15056,6 @@
       <c r="O85" t="n">
         <v>14</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.02925709302693968</v>
       </c>
@@ -15297,9 +15201,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -15989,9 +15890,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -16533,9 +16431,6 @@
       <c r="O93" t="n">
         <v>8</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.01671833887253696</v>
       </c>
@@ -16681,9 +16576,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -17373,9 +17265,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -17917,9 +17806,6 @@
       <c r="O101" t="n">
         <v>8</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.01666440395306741</v>
       </c>
@@ -18065,9 +17951,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -18757,9 +18640,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -19301,9 +19181,6 @@
       <c r="O109" t="n">
         <v>16</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.03332880790613483</v>
       </c>
@@ -19449,9 +19326,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -20141,9 +20015,6 @@
       <c r="O114" t="n">
         <v>1</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -20685,9 +20556,6 @@
       <c r="O117" t="n">
         <v>18</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.03749490889440169</v>
       </c>
@@ -20833,9 +20701,6 @@
       <c r="O118" t="n">
         <v>7</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.1501986699264069</v>
       </c>
@@ -21525,9 +21390,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -22069,9 +21931,6 @@
       <c r="O125" t="n">
         <v>14</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.02916270691786797</v>
       </c>
@@ -22217,9 +22076,6 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -22909,9 +22765,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -23453,9 +23306,6 @@
       <c r="O133" t="n">
         <v>16</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.03332880790613483</v>
       </c>
@@ -23601,9 +23451,6 @@
       <c r="O134" t="n">
         <v>1</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -24293,9 +24140,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -24837,9 +24681,6 @@
       <c r="O141" t="n">
         <v>34</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.07082371680053651</v>
       </c>
@@ -24985,9 +24826,6 @@
       <c r="O142" t="n">
         <v>3</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.06437085853988869</v>
       </c>
@@ -25677,9 +25515,6 @@
       <c r="O146" t="n">
         <v>1</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -26221,9 +26056,6 @@
       <c r="O149" t="n">
         <v>21</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.04374406037680197</v>
       </c>
@@ -26369,9 +26201,6 @@
       <c r="O150" t="n">
         <v>2</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.04291390569325913</v>
       </c>
@@ -27061,9 +26890,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -27605,9 +27431,6 @@
       <c r="O157" t="n">
         <v>23</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.04791016136506882</v>
       </c>
@@ -27753,9 +27576,6 @@
       <c r="O158" t="n">
         <v>5</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.1072847642331478</v>
       </c>
@@ -28445,9 +28265,6 @@
       <c r="O162" t="n">
         <v>1</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -28989,9 +28806,6 @@
       <c r="O165" t="n">
         <v>14</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.02916270691786797</v>
       </c>
@@ -29137,9 +28951,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -29829,9 +29640,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -30373,9 +30181,6 @@
       <c r="O173" t="n">
         <v>8</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.01666440395306741</v>
       </c>
@@ -30521,9 +30326,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -31213,9 +31015,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -31757,9 +31556,6 @@
       <c r="O181" t="n">
         <v>16</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.03332880790613483</v>
       </c>
@@ -31905,9 +31701,6 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0</v>
       </c>
@@ -32597,9 +32390,6 @@
       <c r="O186" t="n">
         <v>1</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -33141,9 +32931,6 @@
       <c r="O189" t="n">
         <v>12</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.02499660592960112</v>
       </c>
@@ -33289,9 +33076,6 @@
       <c r="O190" t="n">
         <v>2</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.04291390569325913</v>
       </c>
@@ -33981,9 +33765,6 @@
       <c r="O194" t="n">
         <v>3</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.05672460770206724</v>
       </c>
@@ -34525,9 +34306,6 @@
       <c r="O197" t="n">
         <v>17</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.03528572831253259</v>
       </c>
@@ -34673,9 +34451,6 @@
       <c r="O198" t="n">
         <v>3</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.06370765829760396</v>
       </c>
@@ -35365,9 +35140,6 @@
       <c r="O202" t="n">
         <v>1</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -35909,9 +35681,6 @@
       <c r="O205" t="n">
         <v>17</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.03528572831253259</v>
       </c>
@@ -36057,9 +35826,6 @@
       <c r="O206" t="n">
         <v>2</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -36601,9 +36367,6 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0</v>
       </c>
@@ -37145,9 +36908,6 @@
       <c r="O212" t="n">
         <v>30</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.06226893231623398</v>
       </c>
@@ -37293,9 +37053,6 @@
       <c r="O213" t="n">
         <v>6</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.1274153165952079</v>
       </c>
@@ -37985,9 +37742,6 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0</v>
       </c>
@@ -38529,9 +38283,6 @@
       <c r="O220" t="n">
         <v>25</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.05189077693019498</v>
       </c>
@@ -38677,9 +38428,6 @@
       <c r="O221" t="n">
         <v>1</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.02123588609920132</v>
       </c>
@@ -39369,9 +39117,6 @@
       <c r="O225" t="n">
         <v>0</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0</v>
       </c>
@@ -39913,9 +39658,6 @@
       <c r="O228" t="n">
         <v>18</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.03736135938974038</v>
       </c>
@@ -40061,9 +39803,6 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0</v>
       </c>
@@ -40753,9 +40492,6 @@
       <c r="O233" t="n">
         <v>2</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -41297,9 +41033,6 @@
       <c r="O236" t="n">
         <v>30</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.06226893231623398</v>
       </c>
@@ -41445,9 +41178,6 @@
       <c r="O237" t="n">
         <v>2</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -42137,9 +41867,6 @@
       <c r="O241" t="n">
         <v>2</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -42681,9 +42408,6 @@
       <c r="O244" t="n">
         <v>18</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.03736135938974038</v>
       </c>
@@ -42829,9 +42553,6 @@
       <c r="O245" t="n">
         <v>4</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.08494354439680528</v>
       </c>
@@ -43521,9 +43242,6 @@
       <c r="O249" t="n">
         <v>0</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0</v>
       </c>
@@ -44065,9 +43783,6 @@
       <c r="O252" t="n">
         <v>20</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0.04151262154415598</v>
       </c>
@@ -44213,9 +43928,6 @@
       <c r="O253" t="n">
         <v>5</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>0.1061794304960066</v>
       </c>
@@ -44905,9 +44617,6 @@
       <c r="O257" t="n">
         <v>0</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0</v>
       </c>
@@ -45449,9 +45158,6 @@
       <c r="O260" t="n">
         <v>18</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.03736135938974038</v>
       </c>
@@ -45597,9 +45303,6 @@
       <c r="O261" t="n">
         <v>2</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -46289,9 +45992,6 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0</v>
       </c>
@@ -46833,9 +46533,6 @@
       <c r="O268" t="n">
         <v>13</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0.02698320400370139</v>
       </c>
@@ -46981,9 +46678,6 @@
       <c r="O269" t="n">
         <v>1</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0.02123588609920132</v>
       </c>
@@ -47673,9 +47367,6 @@
       <c r="O273" t="n">
         <v>1</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -48217,9 +47908,6 @@
       <c r="O276" t="n">
         <v>10</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0.02075631077207799</v>
       </c>
@@ -48365,9 +48053,6 @@
       <c r="O277" t="n">
         <v>1</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0.02123588609920132</v>
       </c>
@@ -49057,9 +48742,6 @@
       <c r="O281" t="n">
         <v>2</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -49601,9 +49283,6 @@
       <c r="O284" t="n">
         <v>7</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0.0145294175404546</v>
       </c>
@@ -49749,9 +49428,6 @@
       <c r="O285" t="n">
         <v>2</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -50589,9 +50265,6 @@
       <c r="O290" t="n">
         <v>0</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0</v>
       </c>
@@ -51133,9 +50806,6 @@
       <c r="O293" t="n">
         <v>12</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0.02481569538138343</v>
       </c>
@@ -51281,9 +50951,6 @@
       <c r="O294" t="n">
         <v>0</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0</v>
       </c>
@@ -52121,9 +51788,6 @@
       <c r="O299" t="n">
         <v>0</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0</v>
       </c>
@@ -52665,9 +52329,6 @@
       <c r="O302" t="n">
         <v>6</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0.01240784769069171</v>
       </c>
@@ -52813,9 +52474,6 @@
       <c r="O303" t="n">
         <v>0</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0</v>
       </c>
@@ -53653,9 +53311,6 @@
       <c r="O308" t="n">
         <v>0</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0</v>
       </c>
@@ -54197,9 +53852,6 @@
       <c r="O311" t="n">
         <v>19</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>0.03929151768719043</v>
       </c>
@@ -54345,9 +53997,6 @@
       <c r="O312" t="n">
         <v>1</v>
       </c>
-      <c r="Q312" t="n">
-        <v>0</v>
-      </c>
       <c r="R312" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -55185,9 +54834,6 @@
       <c r="O317" t="n">
         <v>0</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0</v>
       </c>
@@ -55729,9 +55375,6 @@
       <c r="O320" t="n">
         <v>16</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0.03308759384184457</v>
       </c>
@@ -55877,9 +55520,6 @@
       <c r="O321" t="n">
         <v>1</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -56717,9 +56357,6 @@
       <c r="O326" t="n">
         <v>0</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0</v>
       </c>
@@ -57261,9 +56898,6 @@
       <c r="O329" t="n">
         <v>19</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>0.03929151768719043</v>
       </c>
@@ -57409,9 +57043,6 @@
       <c r="O330" t="n">
         <v>2</v>
       </c>
-      <c r="Q330" t="n">
-        <v>0</v>
-      </c>
       <c r="R330" t="n">
         <v>0.04194542019978184</v>
       </c>
@@ -58249,9 +57880,6 @@
       <c r="O335" t="n">
         <v>0</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>0</v>
       </c>
@@ -58793,9 +58421,6 @@
       <c r="O338" t="n">
         <v>31</v>
       </c>
-      <c r="Q338" t="n">
-        <v>0</v>
-      </c>
       <c r="R338" t="n">
         <v>0.06410721306857385</v>
       </c>
@@ -58941,9 +58566,6 @@
       <c r="O339" t="n">
         <v>2</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0.04194542019978184</v>
       </c>
@@ -59781,9 +59403,6 @@
       <c r="O344" t="n">
         <v>1</v>
       </c>
-      <c r="Q344" t="n">
-        <v>0</v>
-      </c>
       <c r="R344" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -60325,9 +59944,6 @@
       <c r="O347" t="n">
         <v>23</v>
       </c>
-      <c r="Q347" t="n">
-        <v>0</v>
-      </c>
       <c r="R347" t="n">
         <v>0.04756341614765157</v>
       </c>
@@ -60473,9 +60089,6 @@
       <c r="O348" t="n">
         <v>0</v>
       </c>
-      <c r="Q348" t="n">
-        <v>0</v>
-      </c>
       <c r="R348" t="n">
         <v>0</v>
       </c>
@@ -61313,9 +60926,6 @@
       <c r="O353" t="n">
         <v>0</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>0</v>
       </c>
@@ -61857,9 +61467,6 @@
       <c r="O356" t="n">
         <v>15</v>
       </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
       <c r="R356" t="n">
         <v>0.03101961922672929</v>
       </c>
@@ -62005,9 +61612,6 @@
       <c r="O357" t="n">
         <v>1</v>
       </c>
-      <c r="Q357" t="n">
-        <v>0</v>
-      </c>
       <c r="R357" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -62845,9 +62449,6 @@
       <c r="O362" t="n">
         <v>0</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>0</v>
       </c>
@@ -63389,9 +62990,6 @@
       <c r="O365" t="n">
         <v>15</v>
       </c>
-      <c r="Q365" t="n">
-        <v>0</v>
-      </c>
       <c r="R365" t="n">
         <v>0.03101961922672929</v>
       </c>
@@ -63537,9 +63135,6 @@
       <c r="O366" t="n">
         <v>5</v>
       </c>
-      <c r="Q366" t="n">
-        <v>0</v>
-      </c>
       <c r="R366" t="n">
         <v>0.1048635504994546</v>
       </c>
@@ -64377,9 +63972,6 @@
       <c r="O371" t="n">
         <v>1</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -64921,9 +64513,6 @@
       <c r="O374" t="n">
         <v>10</v>
       </c>
-      <c r="Q374" t="n">
-        <v>0</v>
-      </c>
       <c r="R374" t="n">
         <v>0.02067974615115285</v>
       </c>
@@ -65069,9 +64658,6 @@
       <c r="O375" t="n">
         <v>0</v>
       </c>
-      <c r="Q375" t="n">
-        <v>0</v>
-      </c>
       <c r="R375" t="n">
         <v>0</v>
       </c>
@@ -65761,9 +65347,6 @@
       <c r="O379" t="n">
         <v>0</v>
       </c>
-      <c r="Q379" t="n">
-        <v>0</v>
-      </c>
       <c r="R379" t="n">
         <v>0</v>
       </c>
@@ -66305,9 +65888,6 @@
       <c r="O382" t="n">
         <v>6</v>
       </c>
-      <c r="Q382" t="n">
-        <v>0</v>
-      </c>
       <c r="R382" t="n">
         <v>0.01240784769069171</v>
       </c>
@@ -66453,9 +66033,6 @@
       <c r="O383" t="n">
         <v>2</v>
       </c>
-      <c r="Q383" t="n">
-        <v>0</v>
-      </c>
       <c r="R383" t="n">
         <v>0.04194542019978184</v>
       </c>
@@ -67293,9 +66870,6 @@
       <c r="O388" t="n">
         <v>0</v>
       </c>
-      <c r="Q388" t="n">
-        <v>0</v>
-      </c>
       <c r="R388" t="n">
         <v>0</v>
       </c>
@@ -67837,9 +67411,6 @@
       <c r="O391" t="n">
         <v>16</v>
       </c>
-      <c r="Q391" t="n">
-        <v>0</v>
-      </c>
       <c r="R391" t="n">
         <v>0.03308759384184457</v>
       </c>
@@ -67985,9 +67556,6 @@
       <c r="O392" t="n">
         <v>2</v>
       </c>
-      <c r="Q392" t="n">
-        <v>0</v>
-      </c>
       <c r="R392" t="n">
         <v>0.04194542019978184</v>
       </c>
@@ -68825,9 +68393,6 @@
       <c r="O397" t="n">
         <v>0</v>
       </c>
-      <c r="Q397" t="n">
-        <v>0</v>
-      </c>
       <c r="R397" t="n">
         <v>0</v>
       </c>
@@ -69369,9 +68934,6 @@
       <c r="O400" t="n">
         <v>13</v>
       </c>
-      <c r="Q400" t="n">
-        <v>0</v>
-      </c>
       <c r="R400" t="n">
         <v>0.02677834665399872</v>
       </c>
@@ -69517,9 +69079,6 @@
       <c r="O401" t="n">
         <v>2</v>
       </c>
-      <c r="Q401" t="n">
-        <v>0</v>
-      </c>
       <c r="R401" t="n">
         <v>0.04141968025042339</v>
       </c>
@@ -70357,9 +69916,6 @@
       <c r="O406" t="n">
         <v>0</v>
       </c>
-      <c r="Q406" t="n">
-        <v>0</v>
-      </c>
       <c r="R406" t="n">
         <v>0</v>
       </c>
@@ -70901,9 +70457,6 @@
       <c r="O409" t="n">
         <v>8</v>
       </c>
-      <c r="Q409" t="n">
-        <v>0</v>
-      </c>
       <c r="R409" t="n">
         <v>0.01647898255630691</v>
       </c>
@@ -71049,9 +70602,6 @@
       <c r="O410" t="n">
         <v>0</v>
       </c>
-      <c r="Q410" t="n">
-        <v>0</v>
-      </c>
       <c r="R410" t="n">
         <v>0</v>
       </c>
@@ -71889,9 +71439,6 @@
       <c r="O415" t="n">
         <v>1</v>
       </c>
-      <c r="Q415" t="n">
-        <v>0</v>
-      </c>
       <c r="R415" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -72433,9 +71980,6 @@
       <c r="O418" t="n">
         <v>14</v>
       </c>
-      <c r="Q418" t="n">
-        <v>0</v>
-      </c>
       <c r="R418" t="n">
         <v>0.02883821947353709</v>
       </c>
@@ -72581,9 +72125,6 @@
       <c r="O419" t="n">
         <v>3</v>
       </c>
-      <c r="Q419" t="n">
-        <v>0</v>
-      </c>
       <c r="R419" t="n">
         <v>0.06212952037563508</v>
       </c>
@@ -73421,9 +72962,6 @@
       <c r="O424" t="n">
         <v>1</v>
       </c>
-      <c r="Q424" t="n">
-        <v>0</v>
-      </c>
       <c r="R424" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -73965,9 +73503,6 @@
       <c r="O427" t="n">
         <v>25</v>
       </c>
-      <c r="Q427" t="n">
-        <v>0</v>
-      </c>
       <c r="R427" t="n">
         <v>0.05149682048845908</v>
       </c>
@@ -74113,9 +73648,6 @@
       <c r="O428" t="n">
         <v>1</v>
       </c>
-      <c r="Q428" t="n">
-        <v>0</v>
-      </c>
       <c r="R428" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -74953,9 +74485,6 @@
       <c r="O433" t="n">
         <v>0</v>
       </c>
-      <c r="Q433" t="n">
-        <v>0</v>
-      </c>
       <c r="R433" t="n">
         <v>0</v>
       </c>
@@ -75497,9 +75026,6 @@
       <c r="O436" t="n">
         <v>17</v>
       </c>
-      <c r="Q436" t="n">
-        <v>0</v>
-      </c>
       <c r="R436" t="n">
         <v>0.03501783793215218</v>
       </c>
@@ -75645,9 +75171,6 @@
       <c r="O437" t="n">
         <v>0</v>
       </c>
-      <c r="Q437" t="n">
-        <v>0</v>
-      </c>
       <c r="R437" t="n">
         <v>0</v>
       </c>
@@ -76485,9 +76008,6 @@
       <c r="O442" t="n">
         <v>0</v>
       </c>
-      <c r="Q442" t="n">
-        <v>0</v>
-      </c>
       <c r="R442" t="n">
         <v>0</v>
       </c>
@@ -77029,9 +76549,6 @@
       <c r="O445" t="n">
         <v>13</v>
       </c>
-      <c r="Q445" t="n">
-        <v>0</v>
-      </c>
       <c r="R445" t="n">
         <v>0.02677834665399872</v>
       </c>
@@ -77177,9 +76694,6 @@
       <c r="O446" t="n">
         <v>2</v>
       </c>
-      <c r="Q446" t="n">
-        <v>0</v>
-      </c>
       <c r="R446" t="n">
         <v>0.04141968025042339</v>
       </c>
@@ -78017,9 +77531,6 @@
       <c r="O451" t="n">
         <v>1</v>
       </c>
-      <c r="Q451" t="n">
-        <v>0</v>
-      </c>
       <c r="R451" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -78561,9 +78072,6 @@
       <c r="O454" t="n">
         <v>18</v>
       </c>
-      <c r="Q454" t="n">
-        <v>0</v>
-      </c>
       <c r="R454" t="n">
         <v>0.03707771075169054</v>
       </c>
@@ -78709,9 +78217,6 @@
       <c r="O455" t="n">
         <v>1</v>
       </c>
-      <c r="Q455" t="n">
-        <v>0</v>
-      </c>
       <c r="R455" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -79549,9 +79054,6 @@
       <c r="O460" t="n">
         <v>0</v>
       </c>
-      <c r="Q460" t="n">
-        <v>0</v>
-      </c>
       <c r="R460" t="n">
         <v>0</v>
       </c>
@@ -80093,9 +79595,6 @@
       <c r="O463" t="n">
         <v>14</v>
       </c>
-      <c r="Q463" t="n">
-        <v>0</v>
-      </c>
       <c r="R463" t="n">
         <v>0.02883821947353709</v>
       </c>
@@ -80241,9 +79740,6 @@
       <c r="O464" t="n">
         <v>1</v>
       </c>
-      <c r="Q464" t="n">
-        <v>0</v>
-      </c>
       <c r="R464" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -81081,9 +80577,6 @@
       <c r="O469" t="n">
         <v>0</v>
       </c>
-      <c r="Q469" t="n">
-        <v>0</v>
-      </c>
       <c r="R469" t="n">
         <v>0</v>
       </c>
@@ -81625,9 +81118,6 @@
       <c r="O472" t="n">
         <v>17</v>
       </c>
-      <c r="Q472" t="n">
-        <v>0</v>
-      </c>
       <c r="R472" t="n">
         <v>0.03501783793215218</v>
       </c>
@@ -81773,9 +81263,6 @@
       <c r="O473" t="n">
         <v>0</v>
       </c>
-      <c r="Q473" t="n">
-        <v>0</v>
-      </c>
       <c r="R473" t="n">
         <v>0</v>
       </c>
@@ -82613,9 +82100,6 @@
       <c r="O478" t="n">
         <v>1</v>
       </c>
-      <c r="Q478" t="n">
-        <v>0</v>
-      </c>
       <c r="R478" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -83157,9 +82641,6 @@
       <c r="O481" t="n">
         <v>10</v>
       </c>
-      <c r="Q481" t="n">
-        <v>0</v>
-      </c>
       <c r="R481" t="n">
         <v>0.02059872819538363</v>
       </c>
@@ -83305,9 +82786,6 @@
       <c r="O482" t="n">
         <v>0</v>
       </c>
-      <c r="Q482" t="n">
-        <v>0</v>
-      </c>
       <c r="R482" t="n">
         <v>0</v>
       </c>
@@ -84145,9 +83623,6 @@
       <c r="O487" t="n">
         <v>0</v>
       </c>
-      <c r="Q487" t="n">
-        <v>0</v>
-      </c>
       <c r="R487" t="n">
         <v>0</v>
       </c>
@@ -84689,9 +84164,6 @@
       <c r="O490" t="n">
         <v>6</v>
       </c>
-      <c r="Q490" t="n">
-        <v>0</v>
-      </c>
       <c r="R490" t="n">
         <v>0.01235923691723018</v>
       </c>
@@ -84837,9 +84309,6 @@
       <c r="O491" t="n">
         <v>0</v>
       </c>
-      <c r="Q491" t="n">
-        <v>0</v>
-      </c>
       <c r="R491" t="n">
         <v>0</v>
       </c>
@@ -85677,9 +85146,6 @@
       <c r="O496" t="n">
         <v>0</v>
       </c>
-      <c r="Q496" t="n">
-        <v>0</v>
-      </c>
       <c r="R496" t="n">
         <v>0</v>
       </c>
@@ -86221,9 +85687,6 @@
       <c r="O499" t="n">
         <v>13</v>
       </c>
-      <c r="Q499" t="n">
-        <v>0</v>
-      </c>
       <c r="R499" t="n">
         <v>0.02677834665399872</v>
       </c>
@@ -86367,9 +85830,6 @@
         <v>0</v>
       </c>
       <c r="O500" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q500" t="n">
         <v>0</v>
       </c>
       <c r="R500" t="n">
